--- a/data/trans_dic/IP12B$hueso-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$hueso-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,78</t>
+          <t>0,0; 66,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,9</t>
+          <t>0,0; 52,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,27</t>
+          <t>0,0; 63,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,87</t>
+          <t>0,0; 50,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,37; 54,4</t>
+          <t>6,42; 53,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,64</t>
+          <t>0,0; 23,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,28</t>
+          <t>0,0; 40,17</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,71</t>
+          <t>0,0; 14,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 22,14</t>
+          <t>3,95; 22,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,03</t>
+          <t>0,0; 14,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 14,96</t>
+          <t>1,48; 12,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 15,13</t>
+          <t>1,76; 15,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 12,13</t>
+          <t>1,36; 11,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 13,52</t>
+          <t>3,97; 13,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,09</t>
+          <t>0,94; 8,01</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,98</t>
+          <t>0,0; 31,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,66</t>
+          <t>0,0; 20,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 35,67</t>
+          <t>3,82; 31,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 44,52</t>
+          <t>0,0; 45,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,94</t>
+          <t>0,0; 36,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,84</t>
+          <t>0,0; 16,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 21,8</t>
+          <t>2,68; 23,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 25,44</t>
+          <t>2,59; 23,63</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 16,65</t>
+          <t>2,95; 16,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 13,9</t>
+          <t>2,72; 15,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 12,97</t>
+          <t>2,58; 13,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 15,09</t>
+          <t>1,78; 15,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,19; 16,86</t>
+          <t>5,07; 17,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 14,22</t>
+          <t>1,46; 13,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 12,07</t>
+          <t>3,53; 12,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 12,84</t>
+          <t>4,83; 13,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 11,64</t>
+          <t>3,15; 10,96</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1375</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1387</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1258</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2762</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1258</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3731</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3476</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3505</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3546</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>716; 5938</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4066</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3543</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1391</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3680</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1517</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2582</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2098</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2908</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>6261</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2098</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4314</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1386; 7919</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4518</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>670; 5847</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>639; 5635</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>829; 7041</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>3188; 11196</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>639; 5463</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2253</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2211</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2866</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2923</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2708</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3246</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>640; 5311</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5062</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3404</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3128</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>734; 6411</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>673; 6137</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3398</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4335</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3546</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2904</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6051</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2768</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6302</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>10386</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6314</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1294; 7435</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1665; 9378</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1420; 7590</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>830; 7190</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3225; 11208</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>699; 6273</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3197; 11372</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>6027; 16679</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>3241; 11283</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$hueso-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$hueso-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,01</t>
+          <t>0,0; 66,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,83</t>
+          <t>0,0; 53,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,68</t>
+          <t>0,0; 64,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,32</t>
+          <t>0,0; 56,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,42; 53,22</t>
+          <t>6,05; 48,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,77</t>
+          <t>0,0; 23,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,17</t>
+          <t>0,0; 40,26</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,56</t>
+          <t>0,0; 14,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,95; 22,59</t>
+          <t>3,76; 22,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,32 +803,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,41</t>
+          <t>0,0; 14,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 12,91</t>
+          <t>1,44; 13,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 15,49</t>
+          <t>1,79; 15,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,55</t>
+          <t>1,22; 11,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,97; 13,93</t>
+          <t>3,6; 14,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,01</t>
+          <t>0,94; 8,37</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,51</t>
+          <t>0,0; 30,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,06</t>
+          <t>0,0; 19,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 31,75</t>
+          <t>3,9; 35,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,27 +918,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,13</t>
+          <t>6,05; 43,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,81</t>
+          <t>0,0; 31,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,95</t>
+          <t>0,0; 16,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 23,4</t>
+          <t>2,6; 23,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 23,63</t>
+          <t>2,69; 25,5</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 16,95</t>
+          <t>2,99; 17,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 15,3</t>
+          <t>2,54; 16,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 13,77</t>
+          <t>2,4; 14,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 15,39</t>
+          <t>1,53; 14,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 17,63</t>
+          <t>4,91; 17,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,11</t>
+          <t>1,45; 13,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 12,55</t>
+          <t>3,57; 12,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 13,36</t>
+          <t>5,06; 13,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 10,96</t>
+          <t>2,81; 10,86</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3731</t>
+          <t>0; 3761</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3476</t>
+          <t>0; 3519</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3505</t>
+          <t>0; 3562</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3546</t>
+          <t>0; 3949</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>716; 5938</t>
+          <t>675; 5365</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4066</t>
+          <t>0; 4010</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3543</t>
+          <t>0; 3550</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4314</t>
+          <t>0; 4384</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1386; 7919</t>
+          <t>1318; 7733</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1484,32 +1484,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4518</t>
+          <t>0; 4560</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>670; 5847</t>
+          <t>652; 6001</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>639; 5635</t>
+          <t>651; 5709</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>829; 7041</t>
+          <t>744; 6871</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3188; 11196</t>
+          <t>2894; 11517</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>639; 5463</t>
+          <t>641; 5708</t>
         </is>
       </c>
     </row>
@@ -1632,17 +1632,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2708</t>
+          <t>0; 2661</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3246</t>
+          <t>0; 3163</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>640; 5311</t>
+          <t>652; 5929</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1652,27 +1652,27 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5062</t>
+          <t>679; 4905</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3404</t>
+          <t>0; 2874</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3128</t>
+          <t>0; 3136</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>734; 6411</t>
+          <t>712; 6371</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>673; 6137</t>
+          <t>699; 6623</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1294; 7435</t>
+          <t>1310; 7500</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1665; 9378</t>
+          <t>1559; 9850</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1420; 7590</t>
+          <t>1321; 8031</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>830; 7190</t>
+          <t>713; 6839</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3225; 11208</t>
+          <t>3124; 10867</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>699; 6273</t>
+          <t>692; 6592</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3197; 11372</t>
+          <t>3234; 11278</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6027; 16679</t>
+          <t>6323; 17173</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3241; 11283</t>
+          <t>2894; 11188</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$hueso-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$hueso-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>25,19%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17,85%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>24,33%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>19,65%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>25,19%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17,85%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,54</t>
+          <t>0,0; 63,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 49,87</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 53,48</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,72</t>
+          <t>0,0; 64,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 51,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,05; 48,09</t>
+          <t>6,37; 54,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,44</t>
+          <t>0,0; 24,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,26</t>
+          <t>0,0; 45,28</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,84%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,77%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>4,69%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,8</t>
+          <t>0,0; 15,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 22,06</t>
+          <t>1,47; 14,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>1,76; 15,13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 15,71</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,76; 22,14</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 14,55</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,44; 13,25</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,79; 15,7</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,27</t>
+          <t>1,21; 12,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,6; 14,33</t>
+          <t>3,56; 13,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,37</t>
+          <t>0,93; 8,09</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19,71%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,24%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>7,35%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4,05%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>13,47%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,71%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,55</t>
+          <t>5,81; 44,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 35,45</t>
+          <t>0,0; 30,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 38,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 43,72</t>
+          <t>0,0; 20,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,08</t>
+          <t>3,85; 35,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,99</t>
+          <t>0,0; 18,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 23,25</t>
+          <t>2,68; 21,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 25,5</t>
+          <t>2,99; 25,44</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>7,74%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>7,07%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6,43%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,52%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 17,09</t>
+          <t>1,5; 15,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 16,07</t>
+          <t>4,19; 16,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 14,57</t>
+          <t>1,4; 14,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,64</t>
+          <t>2,91; 16,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,91; 17,1</t>
+          <t>2,48; 13,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 13,77</t>
+          <t>1,54; 12,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 12,45</t>
+          <t>3,64; 12,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 13,76</t>
+          <t>4,84; 12,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 10,86</t>
+          <t>2,74; 11,64</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1205,27 +1205,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1387</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1258</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1375</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1293</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1387</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1258</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3761</t>
+          <t>0; 3483</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0; 3515</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3519</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3562</t>
+          <t>0; 3662</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3949</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3415</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>675; 5365</t>
+          <t>711; 6070</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4010</t>
+          <t>0; 4216</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3550</t>
+          <t>0; 3993</t>
         </is>
       </c>
     </row>
@@ -1368,27 +1368,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1517</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2582</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2098</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1391</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3680</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1517</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2582</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4384</t>
+          <t>0; 4712</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1318; 7733</t>
+          <t>664; 6776</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>639; 5502</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4656</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1319; 7761</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4560</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>652; 6001</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>651; 5709</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>744; 6871</t>
+          <t>736; 7399</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2894; 11517</t>
+          <t>2860; 10866</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>641; 5708</t>
+          <t>634; 5515</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2211</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2253</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2211</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2661</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3163</t>
+          <t>651; 4994</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>652; 5929</t>
+          <t>0; 2861</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3351</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>679; 4905</t>
+          <t>0; 3343</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2874</t>
+          <t>644; 5967</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3136</t>
+          <t>0; 3476</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>712; 6371</t>
+          <t>735; 5972</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>699; 6623</t>
+          <t>776; 6609</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2904</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6051</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2768</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>3398</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>4335</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3546</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2904</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6051</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2768</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1310; 7500</t>
+          <t>702; 7047</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1559; 9850</t>
+          <t>2662; 10719</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1321; 8031</t>
+          <t>669; 6806</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>713; 6839</t>
+          <t>1276; 7306</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3124; 10867</t>
+          <t>1521; 8522</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>692; 6592</t>
+          <t>846; 7152</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3234; 11278</t>
+          <t>3294; 10930</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6323; 17173</t>
+          <t>6044; 16026</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2894; 11188</t>
+          <t>2825; 11984</t>
         </is>
       </c>
     </row>
